--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_damage_number.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_damage_number.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_damage_number" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -536,6 +536,9 @@
     <t>玩家攻击怪物</t>
   </si>
   <si>
+    <t>普通</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -554,6 +557,9 @@
     <t>玩家攻击怪物/玩家攻击玩家</t>
   </si>
   <si>
+    <t>幸运</t>
+  </si>
+  <si>
     <t>3012</t>
   </si>
   <si>
@@ -614,6 +620,9 @@
     <t>卓越一击</t>
   </si>
   <si>
+    <t>卓越</t>
+  </si>
+  <si>
     <t>3013</t>
   </si>
   <si>
@@ -623,6 +632,9 @@
     <t>无视防御</t>
   </si>
   <si>
+    <t>无视</t>
+  </si>
+  <si>
     <t>s#-53#0#0|o#0#0#0|n#20#0#0</t>
   </si>
   <si>
@@ -656,6 +668,9 @@
     <t>反射伤害</t>
   </si>
   <si>
+    <t>反射</t>
+  </si>
+  <si>
     <t>3017</t>
   </si>
   <si>
@@ -704,6 +719,9 @@
     <t>反弹伤害</t>
   </si>
   <si>
+    <t>反弹</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -738,9 +756,38 @@
     </r>
   </si>
   <si>
+    <t>普通-双倍</t>
+  </si>
+  <si>
     <t>幸运一击(双倍)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幸运</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双倍</t>
+    </r>
+  </si>
+  <si>
     <t>s#0#0#0|o#-5.74#8#0|n#20#0#0</t>
   </si>
   <si>
@@ -753,6 +800,32 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>卓越</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双倍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>无视防御</t>
     </r>
     <r>
@@ -779,6 +852,95 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双倍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>致命一击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双倍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>致命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>双倍</t>
+    </r>
+  </si>
+  <si>
+    <t>连击</t>
   </si>
 </sst>
 </file>
@@ -1414,12 +1576,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1953,7 +2115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="10.7142857142857" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.2857142857143" style="2" customWidth="1"/>
@@ -2043,7 +2205,7 @@
       <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
@@ -2155,87 +2317,94 @@
         <v>47</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F5" s="2">
-        <v>80</v>
-      </c>
-      <c r="G5" s="4">
+        <v>60</v>
+      </c>
+      <c r="G5" s="5">
         <v>259</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <v>10005</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:14">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2">
         <v>259</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="F7" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2">
         <v>259</v>
@@ -2244,275 +2413,285 @@
         <v>3013</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:14">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2">
         <v>10001</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:14">
       <c r="A9" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="F9" s="2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2">
         <v>259</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>10002</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:14">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:14">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="E11" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="F11" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2">
         <v>259</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:14">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="F12" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2">
         <v>259</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:14">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="F13" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:14">
       <c r="A14" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -2532,16 +2711,16 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M14" s="2">
         <v>2</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:14">
@@ -2549,13 +2728,15 @@
         <v>119</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="F15" s="2">
         <v>60</v>
       </c>
@@ -2572,16 +2753,16 @@
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M15" s="2">
         <v>2</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2589,37 +2770,40 @@
         <v>501</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G16" s="2">
         <v>259</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2627,13 +2811,16 @@
         <v>601</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="E17" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="F17" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2">
         <v>259</v>
@@ -2645,19 +2832,19 @@
         <v>2</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -2665,37 +2852,40 @@
         <v>602</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="F18" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2">
         <v>259</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I18" s="2">
         <v>2</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -2703,37 +2893,40 @@
         <v>603</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F19" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2">
         <v>259</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I19" s="2">
         <v>2</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -2741,13 +2934,16 @@
         <v>604</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="F20" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2">
         <v>259</v>
@@ -2759,19 +2955,101 @@
         <v>2</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="2">
+        <v>605</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="2">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2">
+        <v>287</v>
+      </c>
+      <c r="H21" s="2">
+        <v>287</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="2">
+        <v>301</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="2">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2">
+        <v>180</v>
+      </c>
+      <c r="H22" s="2">
+        <v>180</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2790,22 +3068,22 @@
     <col min="6" max="6" width="45.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="5:8">
+    <row r="9" spans="4:8">
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="4:8">
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="4:4">
+    <row r="11" spans="4:8">
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="4:4">
+    <row r="12" spans="4:8">
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="4:4">
+    <row r="13" spans="4:8">
       <c r="D13" s="1"/>
     </row>
   </sheetData>
